--- a/tds_contents.xlsx
+++ b/tds_contents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wjc/GitHub/LOCA2_Prep/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6F1746-675E-EC4B-B22F-8A2B9FB111B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F1496C-8731-0347-8347-07D8044F296E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="500" windowWidth="34340" windowHeight="20760" activeTab="4" xr2:uid="{53ABE3C2-C6D8-5C45-9C34-C0912D085DB9}"/>
+    <workbookView xWindow="420" yWindow="7480" windowWidth="34340" windowHeight="20760" activeTab="4" xr2:uid="{53ABE3C2-C6D8-5C45-9C34-C0912D085DB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Historical" sheetId="1" r:id="rId1"/>
